--- a/extenbooks/S214_extenbook.xlsx
+++ b/extenbooks/S214_extenbook.xlsx
@@ -1306,7 +1306,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -2153,11 +2153,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2180,64 +2180,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Chapter 2 series S214</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S214_research.json", "adequacy_report": "Technical/docs/chapters/CH2_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S214_DPR.md", "epr": "Technical/docs/series/S214_EPR.md", "loader": "Technical/code/L01_loaders/L01_S214_load.py", "processor": "Technical/code/P02_processors/P02_S214_construct.py", "validator": "Technical/code/V03_validators/V03_S214_validate.py", "processed": "Technical/data/processed/S214.parquet", "chopped_csv": "Technical/chopped/S214.csv", "extenbook_xlsx": "Technical/extenbooks/S214_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S214_extenbook.xlsx
+++ b/extenbooks/S214_extenbook.xlsx
@@ -620,7 +620,7 @@
         <v>1987</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1657418169009641</v>
+        <v>0.1333911145247685</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         <v>1988</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1829843412678318</v>
+        <v>0.1524409826547828</v>
       </c>
     </row>
     <row r="6">
@@ -636,7 +636,7 @@
         <v>1989</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1997344593841098</v>
+        <v>0.1707868582669549</v>
       </c>
     </row>
     <row r="7">
@@ -644,7 +644,7 @@
         <v>1990</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1867593533413787</v>
+        <v>0.1548897276058338</v>
       </c>
     </row>
     <row r="8">
@@ -652,7 +652,7 @@
         <v>1991</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1647928373839685</v>
+        <v>0.1329859989581053</v>
       </c>
     </row>
     <row r="9">
@@ -660,7 +660,7 @@
         <v>1992</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1648245034315738</v>
+        <v>0.1369183862332644</v>
       </c>
     </row>
     <row r="10">
@@ -668,7 +668,7 @@
         <v>1993</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1742060040887855</v>
+        <v>0.1428586569396873</v>
       </c>
     </row>
     <row r="11">
@@ -676,7 +676,7 @@
         <v>1994</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2052251053068874</v>
+        <v>0.1593077103003342</v>
       </c>
     </row>
     <row r="12">
@@ -684,7 +684,7 @@
         <v>1995</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2261974429882655</v>
+        <v>0.1660640730948256</v>
       </c>
     </row>
     <row r="13">
@@ -692,7 +692,7 @@
         <v>1996</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2009145486554326</v>
+        <v>0.1615147019258411</v>
       </c>
     </row>
     <row r="14">
@@ -700,7 +700,7 @@
         <v>1997</v>
       </c>
       <c r="B14" t="n">
-        <v>0.2035248771119736</v>
+        <v>0.1643967899767723</v>
       </c>
     </row>
     <row r="15">
@@ -708,7 +708,7 @@
         <v>1998</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1897678722316578</v>
+        <v>0.1620946217590785</v>
       </c>
     </row>
     <row r="16">
@@ -716,7 +716,7 @@
         <v>1999</v>
       </c>
       <c r="B16" t="n">
-        <v>0.2087529735456539</v>
+        <v>0.1580662261761706</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +724,7 @@
         <v>2000</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1889308839583746</v>
+        <v>0.1425433373738975</v>
       </c>
     </row>
     <row r="18">
@@ -732,7 +732,7 @@
         <v>2001</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1786968327629364</v>
+        <v>0.1306121933286774</v>
       </c>
     </row>
     <row r="19">
@@ -740,7 +740,7 @@
         <v>2002</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1786974437388394</v>
+        <v>0.1259173499972075</v>
       </c>
     </row>
     <row r="20">
@@ -748,7 +748,7 @@
         <v>2003</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1801430559776363</v>
+        <v>0.1343101390978362</v>
       </c>
     </row>
     <row r="21">
@@ -756,7 +756,7 @@
         <v>2004</v>
       </c>
       <c r="B21" t="n">
-        <v>0.2004632908035843</v>
+        <v>0.1663628506433334</v>
       </c>
     </row>
     <row r="22">
@@ -764,7 +764,7 @@
         <v>2005</v>
       </c>
       <c r="B22" t="n">
-        <v>0.2131220509733661</v>
+        <v>0.1798911451405038</v>
       </c>
     </row>
     <row r="23"/>
@@ -809,7 +809,7 @@
         <v>1987</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1657418169009641</v>
+        <v>0.1333911145247685</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>1988</v>
       </c>
       <c r="B29" t="n">
-        <v>0.1829843412678318</v>
+        <v>0.1524409826547828</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>1989</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1997344593841098</v>
+        <v>0.1707868582669549</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>1990</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1867593533413787</v>
+        <v>0.1548897276058338</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>1991</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1647928373839685</v>
+        <v>0.1329859989581053</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>1992</v>
       </c>
       <c r="B33" t="n">
-        <v>0.1648245034315738</v>
+        <v>0.1369183862332644</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>1993</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1742060040887855</v>
+        <v>0.1428586569396873</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>1994</v>
       </c>
       <c r="B35" t="n">
-        <v>0.2052251053068874</v>
+        <v>0.1593077103003342</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>1995</v>
       </c>
       <c r="B36" t="n">
-        <v>0.2261974429882655</v>
+        <v>0.1660640730948256</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>1996</v>
       </c>
       <c r="B37" t="n">
-        <v>0.2009145486554326</v>
+        <v>0.1615147019258411</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>1997</v>
       </c>
       <c r="B38" t="n">
-        <v>0.2035248771119736</v>
+        <v>0.1643967899767723</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>1998</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1897678722316578</v>
+        <v>0.1620946217590785</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>1999</v>
       </c>
       <c r="B40" t="n">
-        <v>0.2087529735456539</v>
+        <v>0.1580662261761706</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>2000</v>
       </c>
       <c r="B41" t="n">
-        <v>0.1889308839583746</v>
+        <v>0.1425433373738975</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>2001</v>
       </c>
       <c r="B42" t="n">
-        <v>0.1786968327629364</v>
+        <v>0.1306121933286774</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>2002</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1786974437388394</v>
+        <v>0.1259173499972075</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>2003</v>
       </c>
       <c r="B44" t="n">
-        <v>0.1801430559776363</v>
+        <v>0.1343101390978362</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>2004</v>
       </c>
       <c r="B45" t="n">
-        <v>0.2004632908035843</v>
+        <v>0.1663628506433334</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>2005</v>
       </c>
       <c r="B46" t="n">
-        <v>0.2131220509733661</v>
+        <v>0.1798911451405038</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>In Shaikh (2016) the series appears as **Figure 2.14** in Chapter 2 ("The Wealth of Nations: A Long View").</t>
+          <t>In Shaikh (2016) the series appears as **Figure 2.12** in Chapter 2 ("Turbulent Trends and Hidden Structures").</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>- Book reference: Shaikh (2016), Ch. 2, Figure 2.14</t>
+          <t>- Book reference: Shaikh (2016), Ch. 2, Figure 2.12</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-18T23:19:43.765529+00:00</t>
+          <t>2026-07-02T06:21:46.891264+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S214_extenbook.xlsx
+++ b/extenbooks/S214_extenbook.xlsx
@@ -1253,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A117"/>
+  <dimension ref="A1:A150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1306,7 +1306,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Status**: extension_only_validated</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>**Series**: S214 -- Average Rates of Profit in US Manufacturing, 1960-1989</t>
+          <t>**Series**: S214 -- Average Rates of Profit in US Manufacturing (post-book, 1987-2005)</t>
         </is>
       </c>
     </row>
@@ -1685,213 +1685,436 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>**Extension status**: `data_unavailable`</t>
+          <t>**Extension status**: `shipped` (Shaikh Appendix-7 companion data; NOT a live-API extension)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t>**Validation class**: `extension_only` (book period 1960-1989 genuinely `data_unavailable`)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-wave2-ch2</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>**Rewritten**: 2026-07-10 (P1.1 remediation, campaign v1.6) to describe what actually ships</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>**Related**: `S214_DPR.md`, `Technical/research/S214_research.json`</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr"/>
-    </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr"/>
-    </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>## 1. Classification</t>
-        </is>
-      </c>
+      <c r="A86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>## 1. What this series actually is</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Per the playbook content-type rule, S214 is classified `formula`. Extension recipe applied: per the Anu framework rule on lazy splices, this dictates the extension method below.</t>
-        </is>
-      </c>
+      <c r="A88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>S214 ships a single subseries, `S214-EXT` (`role: post_book_only`), covering **1987-2005**.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>## 2. Method</t>
+          <t>It is the **mean across 12 US manufacturing industries** of the average rate of profit, taken</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>directly from Shaikh's own Appendix-7 companion workbook</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OECD STAN with sector crosswalk + BEA GDP-by-industry + Fixed-Asset Tables; deferred.</t>
+          <t>`SalvagedInputs/book_data/ShaikhChoppedTables/Appendix7_ropdataUSind.xlsx`. This is Shaikh's</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>own author data, not a modern reconstruction and not a live-API extension.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>## 3. No-Proxy disclosure</t>
-        </is>
-      </c>
+      <c r="A94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>The **book period 1960-1989** (Fig 2.12 / Fig 2.14 panel) is genuinely `data_unavailable`:</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>No proxies used. All extension sources are the same agency/program as the original.</t>
+          <t>the original inputs (anwarshaikhecon.org Appendix 7.2 + OECD ISDB 1994 vintage) are not in</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>`SalvagedInputs/`. Per the no-fabrication rule, no book-period values are synthesized. Because</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>## 4. No-Synthetic disclosure</t>
+          <t>no book-window observation was ever validated against book truth, the registry status is</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>`validated:extension_only` (NOT `book_period_validated`) and `validation_class: extension_only`.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>No synthetic, interpolated, or placeholder values are introduced. Where the API returns NaN, the NaN propagates to the published series.</t>
-        </is>
-      </c>
+      <c r="A100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr"/>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>## 2. Method (as shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>## 5. Failure-mode table</t>
-        </is>
-      </c>
+      <c r="A102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>`L01_S214.py` reads the Appendix-7 workbook and averages the 12 manufacturing-industry columns:</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>| Failure | Detection | Action |</t>
+          <t>**Chemicals, Electr.Equ., Fab.Metal., Food, Mach., Paper, Petroleum, Plastic, Prim.Metal.,</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>|---|---|---|</t>
+          <t>Printing, Text.Mills, Wood** (workbook header spellings). `P02_S214.py` is a pass-through;</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>| API key not set | `S00_config.have_key` returns False | Loader returns `degraded`; processor publishes book period only; registry stamped `extension_status: api_key_missing` |</t>
+          <t>`O06` writes the chopped CSV and extenbook. `splice_method = not_applicable_book_data_unavailable`</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>| API non-200 | `S00_apis._retry_get` raises after 3 retries | Same degradation as above |</t>
+          <t>because there is no book segment to splice with.</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>| Overlap year NaN | Processor checks pre-splice | Walk back overlap year (e.g. 2010 -&gt; 2009 -&gt; 2008); fail hard if no valid overlap in 5-year window |</t>
-        </is>
-      </c>
+      <c r="A108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>| Source URL discontinued | Phase 4 adequacy URL check | EPR documents the substitute (see section 3) |</t>
+          <t>**Motor Vehicles is genuinely absent** from this Appendix-7 panel, so the recoverable</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>manufacturing set is 12 industries (not the 13 an earlier draft named).</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>## 6. CD2 divergence pre-disclosure</t>
-        </is>
-      </c>
+      <c r="A111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr"/>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>## 3. The 2026-07-10 correction (F-4C-02 CRITICAL)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>CD2's predecessor series may diverge from S214 due to (a) different extension anchor, (b) different proxy selection, or (c) a different vintage of the underlying source. Divergence is reported informationally in V03 and never causes a FAIL.</t>
-        </is>
-      </c>
+      <c r="A113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Before this fix, the loader used a hard-coded industry list whose spellings did not match the</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>## 7. Extension status</t>
+          <t>workbook headers. The `have = [c for c in MFG_INDUSTRIES if c in df.columns]` intersection</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>silently kept only **6 of 12** columns (Chemicals, Electr.Equ., Fab.Metal., Food, Paper, Wood)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Current: `data_unavailable`. See DPR caveats for rationale.</t>
+          <t>and dropped the other 6 real manufacturing industries (Machinery, Petroleum, Plastics, Primary</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Metals, Printing, Textiles) because they are spelled differently in the file. The shipped series</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>was therefore a **6-of-12-industry mean**, ~20-42% off the correct manufacturing average every</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>year. The loader now uses an explicit normalization mapping with a hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>`assert len(matched) == 12` guard, so any future header drift FAILS the run loudly instead of</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>silently shrinking the average. See `Technical/anu_framework_review/findings/F-4C-02.md`</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>(Adversarial verification / VERIFY_4C).</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>## 4. No-Proxy / No-Synthetic disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>No proxies. No synthetic, interpolated, or placeholder values. The 12-industry mean is a faithful</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>replication of Shaikh's Appendix-7 companion data. The book period is left empty (not filled).</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>## 5. Independent validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>`validation.independent_anchors` carries three hand-recomputed 12-industry means (1990, 1996,</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2002) taken directly from the raw workbook, independent of the loader path. They were proven RED</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>against the pre-fix (6-column) data and GREEN against the corrected output (evidence:</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>`Technical/remediation_v16/evidence/P1.1_S214_S215.md`). `validation.reference_values` are</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>regression guards only (they round-trip against the corrected chopped) — not an independent check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>## 6. Deferred future extension (NOT shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>A modern extension via **OECD STAN** (ISIC Rev3 -&gt; Rev4 + NAICS crosswalk) + BEA GDP-by-industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>+ Fixed-Asset Tables remains a **deferred, unbuilt** long-term target (scope decision required;</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>OECD ISDB 1994 vintage discontinued). Nothing from OECD STAN currently ships in S214.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>## 7. Failure-mode table</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>| Failure | Detection | Action |</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>|---|---|---|</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>| Appendix-7 workbook missing | `CHOPPED.exists()` False in L01 | Loader returns `FAIL`; no data shipped |</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>| Manufacturing header drift | `assert len(matched) == 12` in L01 | Run FAILS loudly (never a silent partial average) — this is the F-4C-02 guard |</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>| Book period requested | book_period_status = `data_unavailable` | No synthesis; 1960-1989 stays empty until the source is recovered to SalvagedInputs |</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2056,89 +2279,143 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PASS_DATA_UNAVAILABLE</t>
+          <t>PASS_EXTENSION_ONLY</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>book_period</t>
+          <t>validation_class</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[1960, 1989]</t>
+          <t>extension_only</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>book_period_status</t>
+          <t>check</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>data_unavailable</t>
+          <t>full_series_recompute_vs_raw_Appendix7 (F-P2.4-01)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>reason</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>anwarshaikhecon.org App 7.2 / OECD ISDB 1994 not in SalvagedInputs; per anu-framework no-fabrication rule, book values are not synthesized.</t>
-        </is>
+          <t>n_years_checked</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>post_book_rows</t>
+          <t>max_abs_err</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>post_book_range</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>[1987, 2005]</t>
-        </is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1e-06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>remediation</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>When App 7.2 replica is added to SalvagedInputs, re-run L01 to populate 1960-1989.</t>
-        </is>
+          <t>n_mismatches</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>mismatches</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>extension_range</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[1987, 2005]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>book_period</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[1960, 1989]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>book_period_status</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>data_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Post-book 12-industry ROP average (1987-2005) recompute-verified against raw Appendix7_ropdataUSind.xlsx at every year. Book period 1960-1989 remains data_unavailable (anwarshaikhecon.org App 7.2 / OECD ISDB 1994 not in SalvagedInputs); no values fabricated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>validated_at</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-07-02T06:21:46.891264+00:00</t>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-11T03:44:24.475635+00:00</t>
         </is>
       </c>
     </row>
@@ -2153,11 +2430,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2180,6 +2457,150 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>extension_only_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>extension_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Ships the author's verifiable Appendix-7 industry average (1987-2005); book-period 1960-1989 source unavailable, no values fabricated. Reconstructs Fig.2.12 panel; publishable as documented post-book segment.", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S214_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S214_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 2026-05-27 PC-fix: name corrected to actual period/form. Book Fig2.12 plots a ~12-industry panel over 1960-1989; our series is the single-aggregate 1987-2005 Appendix-7 UPDATE (not a reproduction of that figure). The 1960-89 per-industry panel is a documented coverage gap (data-acquisition for v1.x).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rate_decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
